--- a/results/Int Task Remove ACC -0.2/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_4_permute.xlsx
@@ -440,37 +440,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7691981723349859</v>
+        <v>0.7843983274516872</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7785967478410996</v>
+        <v>0.7822555506312159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7847181109497838</v>
+        <v>0.7896882948077247</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7892424169761835</v>
+        <v>0.7869024368866855</v>
       </c>
     </row>
     <row r="6">
@@ -480,217 +480,217 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7958185465333567</v>
+        <v>0.7873863497302822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7936644005516731</v>
+        <v>0.7831437921899237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.795289157044911</v>
+        <v>0.7819372141172736</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8020763395765876</v>
+        <v>0.783855088257765</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8075595826732329</v>
+        <v>0.7940964286777377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8085071505822665</v>
+        <v>0.7994773493234729</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8141584505528305</v>
+        <v>0.7739637112911067</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8101635340148767</v>
+        <v>0.7752498734922425</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7987724613283149</v>
+        <v>0.7724363161602498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7892943016937156</v>
+        <v>0.7780030709137995</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7666638829447698</v>
+        <v>0.7907282629906103</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7600511653596955</v>
+        <v>0.7907282629906103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7600511653596955</v>
+        <v>0.7753763812497313</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7681383597979845</v>
+        <v>0.726587176247631</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7612577434323456</v>
+        <v>0.7160363879306639</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7619463011777625</v>
+        <v>0.7252303185349576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.763998124708536</v>
+        <v>0.7267413834160732</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7324164552691721</v>
+        <v>0.7137799194980701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7333071773721445</v>
+        <v>0.7160136496082394</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7137468455745437</v>
+        <v>0.7160136496082394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7186665916991066</v>
+        <v>0.6800302543715459</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7202799790311325</v>
+        <v>0.6893947223940229</v>
       </c>
     </row>
     <row r="28">
@@ -700,627 +700,627 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7376836843027852</v>
+        <v>0.6992253260262011</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7207979993583659</v>
+        <v>0.7103168729928262</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7164051621779841</v>
+        <v>0.6893996834825519</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.716732387308874</v>
+        <v>0.6810964749812305</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.647391873075511</v>
+        <v>0.6810964749812305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6630966122380131</v>
+        <v>0.6641628328476978</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6786556194249768</v>
+        <v>0.6628539323241376</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6808349842733494</v>
+        <v>0.6753996983658175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6846366250706956</v>
+        <v>0.6717685949866548</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6748791974943196</v>
+        <v>0.6723207227975248</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6741906397489028</v>
+        <v>0.6700276663370299</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6792443352637481</v>
+        <v>0.6558027785403154</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.675269676503954</v>
+        <v>0.6451773671833916</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6856488938426276</v>
+        <v>0.6263421811591088</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6804360300708113</v>
+        <v>0.6269966314208888</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5902064391621713</v>
+        <v>0.6269966314208888</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.583593721577097</v>
+        <v>0.5911986568679656</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5629785383310237</v>
+        <v>0.5860540080634226</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5633057634619137</v>
+        <v>0.5863926023555248</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5633057634619137</v>
+        <v>0.5848929066356212</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5722382033583262</v>
+        <v>0.5868903649045982</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5644302768618138</v>
+        <v>0.5945707500835117</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5551542815847701</v>
+        <v>0.6102093413989609</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5505390222686727</v>
+        <v>0.6377683948894173</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5559703806477859</v>
+        <v>0.6300514216826028</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5566134617483538</v>
+        <v>0.5852769775725725</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5655004249999173</v>
+        <v>0.5859996428016259</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5667865872010531</v>
+        <v>0.5779856244191393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5674410374628331</v>
+        <v>0.5407146199971556</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5523432047970419</v>
+        <v>0.5220350881254692</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5500753672032359</v>
+        <v>0.5147125214567079</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5580993077627806</v>
+        <v>0.5790650745982345</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5586628047348629</v>
+        <v>0.5679532698534495</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5543975088720801</v>
+        <v>0.5637448197967276</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5546856654308044</v>
+        <v>0.627738520867992</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5460413820931164</v>
+        <v>0.6161996490856714</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5457141569622262</v>
+        <v>0.6186266549364485</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5313617278479129</v>
+        <v>0.616401813443227</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5366630643651625</v>
+        <v>0.5767343965497282</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5385582001832295</v>
+        <v>0.5290821076688507</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5404760743237209</v>
+        <v>0.4876094746868726</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5391671738001608</v>
+        <v>0.5053681045003687</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5392126504450097</v>
+        <v>0.5053681045003687</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5392126504450097</v>
+        <v>0.5053681045003687</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.552042645516995</v>
+        <v>0.5042613683343642</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5526629882951385</v>
+        <v>0.5042613683343642</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5540173654635476</v>
+        <v>0.5070927029002523</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5474387553621098</v>
+        <v>0.5060655508627333</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5474387553621098</v>
+        <v>0.4997143239855401</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5491089885001968</v>
+        <v>0.5034932264604618</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.545170917768304</v>
+        <v>0.5124508852235632</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5494589519535112</v>
+        <v>0.5036612833343806</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5367653868160727</v>
+        <v>0.5036612833343806</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5420464655551623</v>
+        <v>0.4810813023188128</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.518856477362553</v>
+        <v>0.4783132216316689</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5191382258485943</v>
+        <v>0.4836486656325553</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5086329141764758</v>
+        <v>0.484178055121001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5086215450152637</v>
+        <v>0.4955261317069782</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5040517623440151</v>
+        <v>0.4958217298984961</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5027314926592427</v>
+        <v>0.4923245759096155</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4994137647054933</v>
+        <v>0.4929903953326079</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5007681418739024</v>
+        <v>0.4889183752104328</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5010612595211558</v>
+        <v>0.4907566652224387</v>
       </c>
     </row>
   </sheetData>
